--- a/mode_docx_gen/pmi_ka/ksv1_modes/КСВ_1.xlsx
+++ b/mode_docx_gen/pmi_ka/ksv1_modes/КСВ_1.xlsx
@@ -1179,11 +1179,11 @@
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1494,9 +1494,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1569,16 +1569,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1619,14 +1619,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">

--- a/mode_docx_gen/pmi_ka/ksv1_modes/КСВ_1.xlsx
+++ b/mode_docx_gen/pmi_ka/ksv1_modes/КСВ_1.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>SGF13_lvalh</t>
         </is>
       </c>
     </row>
@@ -1152,8 +1152,8 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
+      <c r="V2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
